--- a/samples/sample-ais-0810000101.xlsx
+++ b/samples/sample-ais-0810000101.xlsx
@@ -1321,6 +1321,48 @@
     <t>198</t>
   </si>
   <si>
+    <t>2026-08-05T22:58:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-08-05T22:59:04.000Z</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>2026-08-05T23:01:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-08-05T23:01:22.000Z</t>
+  </si>
+  <si>
+    <t>2026-08-05T23:03:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-08-05T23:03:41.000Z</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>2026-08-05T23:05:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-08-05T23:05:18.000Z</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>2026-08-05T23:07:00.000Z</t>
+  </si>
+  <si>
+    <t>2026-08-05T23:07:55.000Z</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
     <t>2026-08-06T13:20:00.000Z</t>
   </si>
   <si>
@@ -1976,9 +2018,6 @@
   </si>
   <si>
     <t>2026-08-29T14:25:41.000Z</t>
-  </si>
-  <si>
-    <t>41</t>
   </si>
   <si>
     <t>2026-08-29T16:39:21.000Z</t>
@@ -14472,7 +14511,7 @@
         <v>45</v>
       </c>
       <c r="F216" s="0" t="s">
-        <v>161</v>
+        <v>437</v>
       </c>
       <c r="G216" s="0" t="s">
         <v>24</v>
@@ -14490,16 +14529,16 @@
         <v>26</v>
       </c>
       <c r="L216" s="0" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="M216" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N216" s="0" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="O216" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="P216" s="0" t="s">
         <v>31</v>
@@ -14511,27 +14550,27 @@
         <v>33</v>
       </c>
       <c r="S216" s="0" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B217" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C217" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D217" s="0" t="s">
-        <v>44</v>
+        <v>154</v>
       </c>
       <c r="E217" s="0" t="s">
         <v>70</v>
       </c>
       <c r="F217" s="0" t="s">
-        <v>439</v>
+        <v>158</v>
       </c>
       <c r="G217" s="0" t="s">
         <v>24</v>
@@ -14549,16 +14588,16 @@
         <v>26</v>
       </c>
       <c r="L217" s="0" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="M217" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N217" s="0" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="O217" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="P217" s="0" t="s">
         <v>31</v>
@@ -14570,7 +14609,7 @@
         <v>33</v>
       </c>
       <c r="S217" s="0" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
     </row>
     <row r="218">
@@ -14584,10 +14623,10 @@
         <v>20</v>
       </c>
       <c r="D218" s="0" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E218" s="0" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F218" s="0" t="s">
         <v>442</v>
@@ -14608,7 +14647,7 @@
         <v>26</v>
       </c>
       <c r="L218" s="0" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="M218" s="0" t="s">
         <v>28</v>
@@ -14643,10 +14682,10 @@
         <v>20</v>
       </c>
       <c r="D219" s="0" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E219" s="0" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F219" s="0" t="s">
         <v>445</v>
@@ -14667,7 +14706,7 @@
         <v>26</v>
       </c>
       <c r="L219" s="0" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="M219" s="0" t="s">
         <v>28</v>
@@ -14695,17 +14734,20 @@
       <c r="A220" s="0" t="s">
         <v>446</v>
       </c>
+      <c r="B220" s="0" t="s">
+        <v>447</v>
+      </c>
       <c r="C220" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D220" s="0" t="s">
-        <v>137</v>
+        <v>44</v>
       </c>
       <c r="E220" s="0" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F220" s="0" t="s">
-        <v>23</v>
+        <v>448</v>
       </c>
       <c r="G220" s="0" t="s">
         <v>24</v>
@@ -14723,16 +14765,16 @@
         <v>26</v>
       </c>
       <c r="L220" s="0" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="M220" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N220" s="0" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="O220" s="0" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="P220" s="0" t="s">
         <v>31</v>
@@ -14744,24 +14786,27 @@
         <v>33</v>
       </c>
       <c r="S220" s="0" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="0" t="s">
-        <v>446</v>
+        <v>449</v>
+      </c>
+      <c r="B221" s="0" t="s">
+        <v>450</v>
       </c>
       <c r="C221" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D221" s="0" t="s">
-        <v>137</v>
+        <v>44</v>
       </c>
       <c r="E221" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F221" s="0" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="G221" s="0" t="s">
         <v>24</v>
@@ -14779,16 +14824,16 @@
         <v>26</v>
       </c>
       <c r="L221" s="0" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="M221" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N221" s="0" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="O221" s="0" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="P221" s="0" t="s">
         <v>31</v>
@@ -14800,24 +14845,27 @@
         <v>33</v>
       </c>
       <c r="S221" s="0" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="0" t="s">
-        <v>447</v>
+        <v>451</v>
+      </c>
+      <c r="B222" s="0" t="s">
+        <v>452</v>
       </c>
       <c r="C222" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D222" s="0" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E222" s="0" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F222" s="0" t="s">
-        <v>23</v>
+        <v>453</v>
       </c>
       <c r="G222" s="0" t="s">
         <v>24</v>
@@ -14832,19 +14880,19 @@
         <v>23</v>
       </c>
       <c r="K222" s="0" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="L222" s="0" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="M222" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N222" s="0" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="O222" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="P222" s="0" t="s">
         <v>31</v>
@@ -14856,24 +14904,27 @@
         <v>33</v>
       </c>
       <c r="S222" s="0" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0" t="s">
-        <v>448</v>
+        <v>454</v>
+      </c>
+      <c r="B223" s="0" t="s">
+        <v>455</v>
       </c>
       <c r="C223" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D223" s="0" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="E223" s="0" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F223" s="0" t="s">
-        <v>23</v>
+        <v>456</v>
       </c>
       <c r="G223" s="0" t="s">
         <v>24</v>
@@ -14891,16 +14942,16 @@
         <v>26</v>
       </c>
       <c r="L223" s="0" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="M223" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N223" s="0" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="O223" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="P223" s="0" t="s">
         <v>31</v>
@@ -14912,15 +14963,15 @@
         <v>33</v>
       </c>
       <c r="S223" s="0" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="B224" s="0" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="C224" s="0" t="s">
         <v>20</v>
@@ -14932,7 +14983,7 @@
         <v>70</v>
       </c>
       <c r="F224" s="0" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="G224" s="0" t="s">
         <v>24</v>
@@ -14950,16 +15001,16 @@
         <v>26</v>
       </c>
       <c r="L224" s="0" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="M224" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N224" s="0" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="O224" s="0" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="P224" s="0" t="s">
         <v>31</v>
@@ -14971,27 +15022,24 @@
         <v>33</v>
       </c>
       <c r="S224" s="0" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="0" t="s">
-        <v>452</v>
-      </c>
-      <c r="B225" s="0" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="C225" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D225" s="0" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="E225" s="0" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="F225" s="0" t="s">
-        <v>454</v>
+        <v>23</v>
       </c>
       <c r="G225" s="0" t="s">
         <v>24</v>
@@ -15009,16 +15057,16 @@
         <v>26</v>
       </c>
       <c r="L225" s="0" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="M225" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N225" s="0" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="O225" s="0" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="P225" s="0" t="s">
         <v>31</v>
@@ -15030,21 +15078,21 @@
         <v>33</v>
       </c>
       <c r="S225" s="0" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C226" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D226" s="0" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="E226" s="0" t="s">
-        <v>151</v>
+        <v>22</v>
       </c>
       <c r="F226" s="0" t="s">
         <v>23</v>
@@ -15065,16 +15113,16 @@
         <v>26</v>
       </c>
       <c r="L226" s="0" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="M226" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N226" s="0" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="O226" s="0" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="P226" s="0" t="s">
         <v>31</v>
@@ -15086,12 +15134,12 @@
         <v>33</v>
       </c>
       <c r="S226" s="0" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C227" s="0" t="s">
         <v>20</v>
@@ -15118,19 +15166,19 @@
         <v>23</v>
       </c>
       <c r="K227" s="0" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="L227" s="0" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="M227" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N227" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="O227" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="P227" s="0" t="s">
         <v>31</v>
@@ -15142,27 +15190,24 @@
         <v>33</v>
       </c>
       <c r="S227" s="0" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="0" t="s">
-        <v>457</v>
-      </c>
-      <c r="B228" s="0" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C228" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D228" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E228" s="0" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="F228" s="0" t="s">
-        <v>459</v>
+        <v>23</v>
       </c>
       <c r="G228" s="0" t="s">
         <v>24</v>
@@ -15177,19 +15222,19 @@
         <v>23</v>
       </c>
       <c r="K228" s="0" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="L228" s="0" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="M228" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N228" s="0" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="O228" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="P228" s="0" t="s">
         <v>31</v>
@@ -15201,15 +15246,15 @@
         <v>33</v>
       </c>
       <c r="S228" s="0" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B229" s="0" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C229" s="0" t="s">
         <v>20</v>
@@ -15218,10 +15263,10 @@
         <v>44</v>
       </c>
       <c r="E229" s="0" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="F229" s="0" t="s">
-        <v>306</v>
+        <v>465</v>
       </c>
       <c r="G229" s="0" t="s">
         <v>24</v>
@@ -15265,19 +15310,22 @@
     </row>
     <row r="230">
       <c r="A230" s="0" t="s">
-        <v>462</v>
+        <v>466</v>
+      </c>
+      <c r="B230" s="0" t="s">
+        <v>467</v>
       </c>
       <c r="C230" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D230" s="0" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E230" s="0" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F230" s="0" t="s">
-        <v>23</v>
+        <v>468</v>
       </c>
       <c r="G230" s="0" t="s">
         <v>24</v>
@@ -15295,7 +15343,7 @@
         <v>26</v>
       </c>
       <c r="L230" s="0" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="M230" s="0" t="s">
         <v>28</v>
@@ -15321,16 +15369,16 @@
     </row>
     <row r="231">
       <c r="A231" s="0" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="C231" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D231" s="0" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="E231" s="0" t="s">
-        <v>22</v>
+        <v>151</v>
       </c>
       <c r="F231" s="0" t="s">
         <v>23</v>
@@ -15351,16 +15399,16 @@
         <v>26</v>
       </c>
       <c r="L231" s="0" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="M231" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N231" s="0" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="O231" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="P231" s="0" t="s">
         <v>31</v>
@@ -15372,18 +15420,18 @@
         <v>33</v>
       </c>
       <c r="S231" s="0" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="0" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="C232" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D232" s="0" t="s">
-        <v>137</v>
+        <v>35</v>
       </c>
       <c r="E232" s="0" t="s">
         <v>22</v>
@@ -15433,22 +15481,22 @@
     </row>
     <row r="233">
       <c r="A233" s="0" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="B233" s="0" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="C233" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D233" s="0" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E233" s="0" t="s">
         <v>70</v>
       </c>
       <c r="F233" s="0" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="G233" s="0" t="s">
         <v>24</v>
@@ -15463,19 +15511,19 @@
         <v>23</v>
       </c>
       <c r="K233" s="0" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="L233" s="0" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="M233" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N233" s="0" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="O233" s="0" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="P233" s="0" t="s">
         <v>31</v>
@@ -15487,27 +15535,27 @@
         <v>33</v>
       </c>
       <c r="S233" s="0" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="0" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="B234" s="0" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="C234" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D234" s="0" t="s">
-        <v>296</v>
+        <v>44</v>
       </c>
       <c r="E234" s="0" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F234" s="0" t="s">
-        <v>469</v>
+        <v>306</v>
       </c>
       <c r="G234" s="0" t="s">
         <v>24</v>
@@ -15525,16 +15573,16 @@
         <v>26</v>
       </c>
       <c r="L234" s="0" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="M234" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N234" s="0" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="O234" s="0" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="P234" s="0" t="s">
         <v>31</v>
@@ -15546,27 +15594,24 @@
         <v>33</v>
       </c>
       <c r="S234" s="0" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="0" t="s">
-        <v>470</v>
-      </c>
-      <c r="B235" s="0" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C235" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D235" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E235" s="0" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="F235" s="0" t="s">
-        <v>472</v>
+        <v>23</v>
       </c>
       <c r="G235" s="0" t="s">
         <v>24</v>
@@ -15610,22 +15655,19 @@
     </row>
     <row r="236">
       <c r="A236" s="0" t="s">
-        <v>473</v>
-      </c>
-      <c r="B236" s="0" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C236" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D236" s="0" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="E236" s="0" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="F236" s="0" t="s">
-        <v>475</v>
+        <v>23</v>
       </c>
       <c r="G236" s="0" t="s">
         <v>24</v>
@@ -15669,22 +15711,19 @@
     </row>
     <row r="237">
       <c r="A237" s="0" t="s">
-        <v>476</v>
-      </c>
-      <c r="B237" s="0" t="s">
         <v>477</v>
       </c>
       <c r="C237" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D237" s="0" t="s">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="E237" s="0" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="F237" s="0" t="s">
-        <v>478</v>
+        <v>23</v>
       </c>
       <c r="G237" s="0" t="s">
         <v>24</v>
@@ -15702,16 +15741,16 @@
         <v>26</v>
       </c>
       <c r="L237" s="0" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="M237" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N237" s="0" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="O237" s="0" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="P237" s="0" t="s">
         <v>31</v>
@@ -15723,27 +15762,27 @@
         <v>33</v>
       </c>
       <c r="S237" s="0" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="B238" s="0" t="s">
         <v>479</v>
       </c>
-      <c r="B238" s="0" t="s">
+      <c r="C238" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="D238" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="E238" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="F238" s="0" t="s">
         <v>480</v>
-      </c>
-      <c r="C238" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="D238" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="E238" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="F238" s="0" t="s">
-        <v>481</v>
       </c>
       <c r="G238" s="0" t="s">
         <v>24</v>
@@ -15761,16 +15800,16 @@
         <v>26</v>
       </c>
       <c r="L238" s="0" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="M238" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N238" s="0" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="O238" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="P238" s="0" t="s">
         <v>31</v>
@@ -15782,24 +15821,27 @@
         <v>33</v>
       </c>
       <c r="S238" s="0" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="0" t="s">
+        <v>481</v>
+      </c>
+      <c r="B239" s="0" t="s">
         <v>482</v>
       </c>
       <c r="C239" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D239" s="0" t="s">
-        <v>137</v>
+        <v>296</v>
       </c>
       <c r="E239" s="0" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F239" s="0" t="s">
-        <v>23</v>
+        <v>483</v>
       </c>
       <c r="G239" s="0" t="s">
         <v>24</v>
@@ -15843,19 +15885,22 @@
     </row>
     <row r="240">
       <c r="A240" s="0" t="s">
-        <v>483</v>
+        <v>484</v>
+      </c>
+      <c r="B240" s="0" t="s">
+        <v>485</v>
       </c>
       <c r="C240" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D240" s="0" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E240" s="0" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F240" s="0" t="s">
-        <v>23</v>
+        <v>486</v>
       </c>
       <c r="G240" s="0" t="s">
         <v>24</v>
@@ -15899,19 +15944,22 @@
     </row>
     <row r="241">
       <c r="A241" s="0" t="s">
-        <v>483</v>
+        <v>487</v>
+      </c>
+      <c r="B241" s="0" t="s">
+        <v>488</v>
       </c>
       <c r="C241" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D241" s="0" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E241" s="0" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F241" s="0" t="s">
-        <v>23</v>
+        <v>489</v>
       </c>
       <c r="G241" s="0" t="s">
         <v>24</v>
@@ -15929,7 +15977,7 @@
         <v>26</v>
       </c>
       <c r="L241" s="0" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="M241" s="0" t="s">
         <v>28</v>
@@ -15955,19 +16003,22 @@
     </row>
     <row r="242">
       <c r="A242" s="0" t="s">
-        <v>483</v>
+        <v>490</v>
+      </c>
+      <c r="B242" s="0" t="s">
+        <v>491</v>
       </c>
       <c r="C242" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D242" s="0" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="E242" s="0" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F242" s="0" t="s">
-        <v>23</v>
+        <v>492</v>
       </c>
       <c r="G242" s="0" t="s">
         <v>24</v>
@@ -15985,16 +16036,16 @@
         <v>26</v>
       </c>
       <c r="L242" s="0" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="M242" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N242" s="0" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="O242" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="P242" s="0" t="s">
         <v>31</v>
@@ -16006,24 +16057,27 @@
         <v>33</v>
       </c>
       <c r="S242" s="0" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="0" t="s">
-        <v>484</v>
+        <v>493</v>
+      </c>
+      <c r="B243" s="0" t="s">
+        <v>494</v>
       </c>
       <c r="C243" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D243" s="0" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E243" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F243" s="0" t="s">
-        <v>23</v>
+        <v>495</v>
       </c>
       <c r="G243" s="0" t="s">
         <v>24</v>
@@ -16067,22 +16121,19 @@
     </row>
     <row r="244">
       <c r="A244" s="0" t="s">
-        <v>485</v>
-      </c>
-      <c r="B244" s="0" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="C244" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D244" s="0" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="E244" s="0" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="F244" s="0" t="s">
-        <v>487</v>
+        <v>23</v>
       </c>
       <c r="G244" s="0" t="s">
         <v>24</v>
@@ -16100,16 +16151,16 @@
         <v>26</v>
       </c>
       <c r="L244" s="0" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M244" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N244" s="0" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="O244" s="0" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="P244" s="0" t="s">
         <v>31</v>
@@ -16121,27 +16172,24 @@
         <v>33</v>
       </c>
       <c r="S244" s="0" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="s">
-        <v>488</v>
-      </c>
-      <c r="B245" s="0" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="C245" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D245" s="0" t="s">
-        <v>154</v>
+        <v>35</v>
       </c>
       <c r="E245" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F245" s="0" t="s">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="G245" s="0" t="s">
         <v>24</v>
@@ -16159,16 +16207,16 @@
         <v>26</v>
       </c>
       <c r="L245" s="0" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="M245" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N245" s="0" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="O245" s="0" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="P245" s="0" t="s">
         <v>31</v>
@@ -16180,18 +16228,18 @@
         <v>33</v>
       </c>
       <c r="S245" s="0" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="C246" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D246" s="0" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E246" s="0" t="s">
         <v>22</v>
@@ -16241,13 +16289,13 @@
     </row>
     <row r="247">
       <c r="A247" s="0" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="C247" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D247" s="0" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E247" s="0" t="s">
         <v>22</v>
@@ -16297,22 +16345,19 @@
     </row>
     <row r="248">
       <c r="A248" s="0" t="s">
-        <v>491</v>
-      </c>
-      <c r="B248" s="0" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="C248" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D248" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E248" s="0" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="F248" s="0" t="s">
-        <v>493</v>
+        <v>23</v>
       </c>
       <c r="G248" s="0" t="s">
         <v>24</v>
@@ -16330,7 +16375,7 @@
         <v>26</v>
       </c>
       <c r="L248" s="0" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="M248" s="0" t="s">
         <v>28</v>
@@ -16356,19 +16401,22 @@
     </row>
     <row r="249">
       <c r="A249" s="0" t="s">
-        <v>494</v>
+        <v>499</v>
+      </c>
+      <c r="B249" s="0" t="s">
+        <v>500</v>
       </c>
       <c r="C249" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D249" s="0" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E249" s="0" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F249" s="0" t="s">
-        <v>23</v>
+        <v>501</v>
       </c>
       <c r="G249" s="0" t="s">
         <v>24</v>
@@ -16386,16 +16434,16 @@
         <v>26</v>
       </c>
       <c r="L249" s="0" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="M249" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N249" s="0" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="O249" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="P249" s="0" t="s">
         <v>31</v>
@@ -16407,24 +16455,27 @@
         <v>33</v>
       </c>
       <c r="S249" s="0" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0" t="s">
-        <v>494</v>
+        <v>502</v>
+      </c>
+      <c r="B250" s="0" t="s">
+        <v>503</v>
       </c>
       <c r="C250" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D250" s="0" t="s">
-        <v>35</v>
+        <v>154</v>
       </c>
       <c r="E250" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F250" s="0" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="G250" s="0" t="s">
         <v>24</v>
@@ -16442,16 +16493,16 @@
         <v>26</v>
       </c>
       <c r="L250" s="0" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="M250" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N250" s="0" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="O250" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="P250" s="0" t="s">
         <v>31</v>
@@ -16463,18 +16514,18 @@
         <v>33</v>
       </c>
       <c r="S250" s="0" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="0" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="C251" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D251" s="0" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E251" s="0" t="s">
         <v>22</v>
@@ -16524,22 +16575,19 @@
     </row>
     <row r="252">
       <c r="A252" s="0" t="s">
-        <v>495</v>
-      </c>
-      <c r="B252" s="0" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="C252" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D252" s="0" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E252" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F252" s="0" t="s">
-        <v>497</v>
+        <v>23</v>
       </c>
       <c r="G252" s="0" t="s">
         <v>24</v>
@@ -16557,7 +16605,7 @@
         <v>26</v>
       </c>
       <c r="L252" s="0" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="M252" s="0" t="s">
         <v>28</v>
@@ -16583,19 +16631,22 @@
     </row>
     <row r="253">
       <c r="A253" s="0" t="s">
-        <v>498</v>
+        <v>505</v>
+      </c>
+      <c r="B253" s="0" t="s">
+        <v>506</v>
       </c>
       <c r="C253" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D253" s="0" t="s">
-        <v>137</v>
+        <v>44</v>
       </c>
       <c r="E253" s="0" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F253" s="0" t="s">
-        <v>23</v>
+        <v>507</v>
       </c>
       <c r="G253" s="0" t="s">
         <v>24</v>
@@ -16639,13 +16690,13 @@
     </row>
     <row r="254">
       <c r="A254" s="0" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="C254" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D254" s="0" t="s">
-        <v>137</v>
+        <v>35</v>
       </c>
       <c r="E254" s="0" t="s">
         <v>22</v>
@@ -16669,7 +16720,7 @@
         <v>26</v>
       </c>
       <c r="L254" s="0" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="M254" s="0" t="s">
         <v>28</v>
@@ -16695,13 +16746,13 @@
     </row>
     <row r="255">
       <c r="A255" s="0" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="C255" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D255" s="0" t="s">
-        <v>137</v>
+        <v>35</v>
       </c>
       <c r="E255" s="0" t="s">
         <v>22</v>
@@ -16725,7 +16776,7 @@
         <v>26</v>
       </c>
       <c r="L255" s="0" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="M255" s="0" t="s">
         <v>28</v>
@@ -16751,22 +16802,19 @@
     </row>
     <row r="256">
       <c r="A256" s="0" t="s">
-        <v>499</v>
-      </c>
-      <c r="B256" s="0" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="C256" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D256" s="0" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="E256" s="0" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="F256" s="0" t="s">
-        <v>501</v>
+        <v>23</v>
       </c>
       <c r="G256" s="0" t="s">
         <v>24</v>
@@ -16784,16 +16832,16 @@
         <v>26</v>
       </c>
       <c r="L256" s="0" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="M256" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N256" s="0" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="O256" s="0" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="P256" s="0" t="s">
         <v>31</v>
@@ -16805,24 +16853,27 @@
         <v>33</v>
       </c>
       <c r="S256" s="0" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="0" t="s">
-        <v>502</v>
+        <v>509</v>
+      </c>
+      <c r="B257" s="0" t="s">
+        <v>510</v>
       </c>
       <c r="C257" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D257" s="0" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E257" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F257" s="0" t="s">
-        <v>23</v>
+        <v>511</v>
       </c>
       <c r="G257" s="0" t="s">
         <v>24</v>
@@ -16840,7 +16891,7 @@
         <v>26</v>
       </c>
       <c r="L257" s="0" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="M257" s="0" t="s">
         <v>28</v>
@@ -16866,13 +16917,13 @@
     </row>
     <row r="258">
       <c r="A258" s="0" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="C258" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D258" s="0" t="s">
-        <v>35</v>
+        <v>137</v>
       </c>
       <c r="E258" s="0" t="s">
         <v>22</v>
@@ -16896,7 +16947,7 @@
         <v>26</v>
       </c>
       <c r="L258" s="0" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="M258" s="0" t="s">
         <v>28</v>
@@ -16922,22 +16973,19 @@
     </row>
     <row r="259">
       <c r="A259" s="0" t="s">
-        <v>504</v>
-      </c>
-      <c r="B259" s="0" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="C259" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D259" s="0" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="E259" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F259" s="0" t="s">
-        <v>506</v>
+        <v>23</v>
       </c>
       <c r="G259" s="0" t="s">
         <v>24</v>
@@ -16955,16 +17003,16 @@
         <v>26</v>
       </c>
       <c r="L259" s="0" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="M259" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N259" s="0" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="O259" s="0" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="P259" s="0" t="s">
         <v>31</v>
@@ -16976,27 +17024,24 @@
         <v>33</v>
       </c>
       <c r="S259" s="0" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="B260" s="0" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C260" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D260" s="0" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="E260" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F260" s="0" t="s">
-        <v>481</v>
+        <v>23</v>
       </c>
       <c r="G260" s="0" t="s">
         <v>24</v>
@@ -17014,16 +17059,16 @@
         <v>26</v>
       </c>
       <c r="L260" s="0" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="M260" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N260" s="0" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="O260" s="0" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="P260" s="0" t="s">
         <v>31</v>
@@ -17035,24 +17080,27 @@
         <v>33</v>
       </c>
       <c r="S260" s="0" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="0" t="s">
-        <v>509</v>
+        <v>513</v>
+      </c>
+      <c r="B261" s="0" t="s">
+        <v>514</v>
       </c>
       <c r="C261" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D261" s="0" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="E261" s="0" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F261" s="0" t="s">
-        <v>23</v>
+        <v>515</v>
       </c>
       <c r="G261" s="0" t="s">
         <v>24</v>
@@ -17070,16 +17118,16 @@
         <v>26</v>
       </c>
       <c r="L261" s="0" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="M261" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N261" s="0" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="O261" s="0" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="P261" s="0" t="s">
         <v>31</v>
@@ -17091,12 +17139,12 @@
         <v>33</v>
       </c>
       <c r="S261" s="0" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="0" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="C262" s="0" t="s">
         <v>20</v>
@@ -17123,19 +17171,19 @@
         <v>23</v>
       </c>
       <c r="K262" s="0" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="L262" s="0" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="M262" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N262" s="0" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="O262" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="P262" s="0" t="s">
         <v>31</v>
@@ -17147,27 +17195,24 @@
         <v>33</v>
       </c>
       <c r="S262" s="0" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="0" t="s">
-        <v>511</v>
-      </c>
-      <c r="B263" s="0" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="C263" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D263" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E263" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F263" s="0" t="s">
-        <v>180</v>
+        <v>23</v>
       </c>
       <c r="G263" s="0" t="s">
         <v>24</v>
@@ -17185,7 +17230,7 @@
         <v>26</v>
       </c>
       <c r="L263" s="0" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="M263" s="0" t="s">
         <v>28</v>
@@ -17211,10 +17256,10 @@
     </row>
     <row r="264">
       <c r="A264" s="0" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B264" s="0" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="C264" s="0" t="s">
         <v>20</v>
@@ -17223,10 +17268,10 @@
         <v>44</v>
       </c>
       <c r="E264" s="0" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F264" s="0" t="s">
-        <v>442</v>
+        <v>520</v>
       </c>
       <c r="G264" s="0" t="s">
         <v>24</v>
@@ -17244,16 +17289,16 @@
         <v>26</v>
       </c>
       <c r="L264" s="0" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="M264" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N264" s="0" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="O264" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="P264" s="0" t="s">
         <v>31</v>
@@ -17265,27 +17310,27 @@
         <v>33</v>
       </c>
       <c r="S264" s="0" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="0" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="B265" s="0" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C265" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D265" s="0" t="s">
-        <v>44</v>
+        <v>154</v>
       </c>
       <c r="E265" s="0" t="s">
         <v>45</v>
       </c>
       <c r="F265" s="0" t="s">
-        <v>442</v>
+        <v>495</v>
       </c>
       <c r="G265" s="0" t="s">
         <v>24</v>
@@ -17303,16 +17348,16 @@
         <v>26</v>
       </c>
       <c r="L265" s="0" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="M265" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N265" s="0" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="O265" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="P265" s="0" t="s">
         <v>31</v>
@@ -17324,18 +17369,18 @@
         <v>33</v>
       </c>
       <c r="S265" s="0" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="0" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="C266" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D266" s="0" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E266" s="0" t="s">
         <v>22</v>
@@ -17359,16 +17404,16 @@
         <v>26</v>
       </c>
       <c r="L266" s="0" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="M266" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N266" s="0" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="O266" s="0" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="P266" s="0" t="s">
         <v>31</v>
@@ -17380,27 +17425,24 @@
         <v>33</v>
       </c>
       <c r="S266" s="0" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="0" t="s">
-        <v>518</v>
-      </c>
-      <c r="B267" s="0" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="C267" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D267" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E267" s="0" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="F267" s="0" t="s">
-        <v>520</v>
+        <v>23</v>
       </c>
       <c r="G267" s="0" t="s">
         <v>24</v>
@@ -17415,19 +17457,19 @@
         <v>23</v>
       </c>
       <c r="K267" s="0" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="L267" s="0" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="M267" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N267" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="O267" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="P267" s="0" t="s">
         <v>31</v>
@@ -17439,15 +17481,15 @@
         <v>33</v>
       </c>
       <c r="S267" s="0" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="0" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B268" s="0" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C268" s="0" t="s">
         <v>20</v>
@@ -17456,10 +17498,10 @@
         <v>44</v>
       </c>
       <c r="E268" s="0" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F268" s="0" t="s">
-        <v>523</v>
+        <v>180</v>
       </c>
       <c r="G268" s="0" t="s">
         <v>24</v>
@@ -17477,7 +17519,7 @@
         <v>26</v>
       </c>
       <c r="L268" s="0" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="M268" s="0" t="s">
         <v>28</v>
@@ -17503,10 +17545,10 @@
     </row>
     <row r="269">
       <c r="A269" s="0" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B269" s="0" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C269" s="0" t="s">
         <v>20</v>
@@ -17518,7 +17560,7 @@
         <v>70</v>
       </c>
       <c r="F269" s="0" t="s">
-        <v>526</v>
+        <v>456</v>
       </c>
       <c r="G269" s="0" t="s">
         <v>24</v>
@@ -17562,10 +17604,10 @@
     </row>
     <row r="270">
       <c r="A270" s="0" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B270" s="0" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C270" s="0" t="s">
         <v>20</v>
@@ -17577,7 +17619,7 @@
         <v>45</v>
       </c>
       <c r="F270" s="0" t="s">
-        <v>529</v>
+        <v>456</v>
       </c>
       <c r="G270" s="0" t="s">
         <v>24</v>
@@ -17595,16 +17637,16 @@
         <v>26</v>
       </c>
       <c r="L270" s="0" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="M270" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N270" s="0" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="O270" s="0" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="P270" s="0" t="s">
         <v>31</v>
@@ -17616,27 +17658,24 @@
         <v>33</v>
       </c>
       <c r="S270" s="0" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="0" t="s">
-        <v>530</v>
-      </c>
-      <c r="B271" s="0" t="s">
         <v>531</v>
       </c>
       <c r="C271" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D271" s="0" t="s">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="E271" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F271" s="0" t="s">
-        <v>302</v>
+        <v>23</v>
       </c>
       <c r="G271" s="0" t="s">
         <v>24</v>
@@ -17654,16 +17693,16 @@
         <v>26</v>
       </c>
       <c r="L271" s="0" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="M271" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N271" s="0" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="O271" s="0" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="P271" s="0" t="s">
         <v>31</v>
@@ -17675,7 +17714,7 @@
         <v>33</v>
       </c>
       <c r="S271" s="0" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="272">
@@ -17692,10 +17731,10 @@
         <v>44</v>
       </c>
       <c r="E272" s="0" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="F272" s="0" t="s">
-        <v>302</v>
+        <v>534</v>
       </c>
       <c r="G272" s="0" t="s">
         <v>24</v>
@@ -17713,7 +17752,7 @@
         <v>26</v>
       </c>
       <c r="L272" s="0" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="M272" s="0" t="s">
         <v>28</v>
@@ -17739,22 +17778,22 @@
     </row>
     <row r="273">
       <c r="A273" s="0" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B273" s="0" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C273" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D273" s="0" t="s">
-        <v>296</v>
+        <v>44</v>
       </c>
       <c r="E273" s="0" t="s">
         <v>70</v>
       </c>
       <c r="F273" s="0" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="G273" s="0" t="s">
         <v>24</v>
@@ -17772,7 +17811,7 @@
         <v>26</v>
       </c>
       <c r="L273" s="0" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="M273" s="0" t="s">
         <v>28</v>
@@ -17798,22 +17837,22 @@
     </row>
     <row r="274">
       <c r="A274" s="0" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B274" s="0" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C274" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D274" s="0" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E274" s="0" t="s">
         <v>70</v>
       </c>
       <c r="F274" s="0" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="G274" s="0" t="s">
         <v>24</v>
@@ -17831,16 +17870,16 @@
         <v>26</v>
       </c>
       <c r="L274" s="0" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="M274" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N274" s="0" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="O274" s="0" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="P274" s="0" t="s">
         <v>31</v>
@@ -17852,15 +17891,15 @@
         <v>33</v>
       </c>
       <c r="S274" s="0" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="0" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B275" s="0" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C275" s="0" t="s">
         <v>20</v>
@@ -17872,7 +17911,7 @@
         <v>45</v>
       </c>
       <c r="F275" s="0" t="s">
-        <v>497</v>
+        <v>543</v>
       </c>
       <c r="G275" s="0" t="s">
         <v>24</v>
@@ -17890,16 +17929,16 @@
         <v>26</v>
       </c>
       <c r="L275" s="0" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="M275" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N275" s="0" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="O275" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="P275" s="0" t="s">
         <v>31</v>
@@ -17911,27 +17950,27 @@
         <v>33</v>
       </c>
       <c r="S275" s="0" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="0" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B276" s="0" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C276" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D276" s="0" t="s">
-        <v>74</v>
+        <v>154</v>
       </c>
       <c r="E276" s="0" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F276" s="0" t="s">
-        <v>544</v>
+        <v>302</v>
       </c>
       <c r="G276" s="0" t="s">
         <v>24</v>
@@ -17975,10 +18014,10 @@
     </row>
     <row r="277">
       <c r="A277" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B277" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C277" s="0" t="s">
         <v>20</v>
@@ -17987,10 +18026,10 @@
         <v>44</v>
       </c>
       <c r="E277" s="0" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F277" s="0" t="s">
-        <v>547</v>
+        <v>302</v>
       </c>
       <c r="G277" s="0" t="s">
         <v>24</v>
@@ -18008,16 +18047,16 @@
         <v>26</v>
       </c>
       <c r="L277" s="0" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M277" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N277" s="0" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="O277" s="0" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="P277" s="0" t="s">
         <v>31</v>
@@ -18029,7 +18068,7 @@
         <v>33</v>
       </c>
       <c r="S277" s="0" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="278">
@@ -18043,13 +18082,13 @@
         <v>20</v>
       </c>
       <c r="D278" s="0" t="s">
-        <v>44</v>
+        <v>296</v>
       </c>
       <c r="E278" s="0" t="s">
         <v>70</v>
       </c>
       <c r="F278" s="0" t="s">
-        <v>96</v>
+        <v>550</v>
       </c>
       <c r="G278" s="0" t="s">
         <v>24</v>
@@ -18067,7 +18106,7 @@
         <v>26</v>
       </c>
       <c r="L278" s="0" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="M278" s="0" t="s">
         <v>28</v>
@@ -18093,19 +18132,22 @@
     </row>
     <row r="279">
       <c r="A279" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
+      </c>
+      <c r="B279" s="0" t="s">
+        <v>552</v>
       </c>
       <c r="C279" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D279" s="0" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="E279" s="0" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F279" s="0" t="s">
-        <v>23</v>
+        <v>553</v>
       </c>
       <c r="G279" s="0" t="s">
         <v>24</v>
@@ -18123,16 +18165,16 @@
         <v>26</v>
       </c>
       <c r="L279" s="0" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="M279" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N279" s="0" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="O279" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="P279" s="0" t="s">
         <v>31</v>
@@ -18144,24 +18186,27 @@
         <v>33</v>
       </c>
       <c r="S279" s="0" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="s">
-        <v>551</v>
+        <v>554</v>
+      </c>
+      <c r="B280" s="0" t="s">
+        <v>555</v>
       </c>
       <c r="C280" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D280" s="0" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E280" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F280" s="0" t="s">
-        <v>23</v>
+        <v>511</v>
       </c>
       <c r="G280" s="0" t="s">
         <v>24</v>
@@ -18179,7 +18224,7 @@
         <v>26</v>
       </c>
       <c r="L280" s="0" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="M280" s="0" t="s">
         <v>28</v>
@@ -18205,22 +18250,22 @@
     </row>
     <row r="281">
       <c r="A281" s="0" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B281" s="0" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C281" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D281" s="0" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E281" s="0" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="F281" s="0" t="s">
-        <v>309</v>
+        <v>558</v>
       </c>
       <c r="G281" s="0" t="s">
         <v>24</v>
@@ -18238,16 +18283,16 @@
         <v>26</v>
       </c>
       <c r="L281" s="0" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="M281" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N281" s="0" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="O281" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="P281" s="0" t="s">
         <v>31</v>
@@ -18259,15 +18304,15 @@
         <v>33</v>
       </c>
       <c r="S281" s="0" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="0" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="B282" s="0" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="C282" s="0" t="s">
         <v>20</v>
@@ -18276,10 +18321,10 @@
         <v>44</v>
       </c>
       <c r="E282" s="0" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="F282" s="0" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="G282" s="0" t="s">
         <v>24</v>
@@ -18294,19 +18339,19 @@
         <v>23</v>
       </c>
       <c r="K282" s="0" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="L282" s="0" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="M282" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N282" s="0" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="O282" s="0" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="P282" s="0" t="s">
         <v>31</v>
@@ -18318,15 +18363,15 @@
         <v>33</v>
       </c>
       <c r="S282" s="0" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="0" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="B283" s="0" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="C283" s="0" t="s">
         <v>20</v>
@@ -18335,10 +18380,10 @@
         <v>44</v>
       </c>
       <c r="E283" s="0" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="F283" s="0" t="s">
-        <v>158</v>
+        <v>96</v>
       </c>
       <c r="G283" s="0" t="s">
         <v>24</v>
@@ -18382,22 +18427,19 @@
     </row>
     <row r="284">
       <c r="A284" s="0" t="s">
-        <v>559</v>
-      </c>
-      <c r="B284" s="0" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C284" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D284" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E284" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F284" s="0" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="G284" s="0" t="s">
         <v>24</v>
@@ -18441,22 +18483,19 @@
     </row>
     <row r="285">
       <c r="A285" s="0" t="s">
-        <v>561</v>
-      </c>
-      <c r="B285" s="0" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C285" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D285" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E285" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F285" s="0" t="s">
-        <v>469</v>
+        <v>23</v>
       </c>
       <c r="G285" s="0" t="s">
         <v>24</v>
@@ -18474,16 +18513,16 @@
         <v>26</v>
       </c>
       <c r="L285" s="0" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="M285" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N285" s="0" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="O285" s="0" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="P285" s="0" t="s">
         <v>31</v>
@@ -18495,27 +18534,27 @@
         <v>33</v>
       </c>
       <c r="S285" s="0" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="0" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B286" s="0" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C286" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D286" s="0" t="s">
-        <v>154</v>
+        <v>44</v>
       </c>
       <c r="E286" s="0" t="s">
         <v>45</v>
       </c>
       <c r="F286" s="0" t="s">
-        <v>565</v>
+        <v>309</v>
       </c>
       <c r="G286" s="0" t="s">
         <v>24</v>
@@ -18533,16 +18572,16 @@
         <v>26</v>
       </c>
       <c r="L286" s="0" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M286" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N286" s="0" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="O286" s="0" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="P286" s="0" t="s">
         <v>31</v>
@@ -18554,15 +18593,15 @@
         <v>33</v>
       </c>
       <c r="S286" s="0" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="0" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B287" s="0" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C287" s="0" t="s">
         <v>20</v>
@@ -18571,10 +18610,10 @@
         <v>44</v>
       </c>
       <c r="E287" s="0" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F287" s="0" t="s">
-        <v>288</v>
+        <v>570</v>
       </c>
       <c r="G287" s="0" t="s">
         <v>24</v>
@@ -18589,19 +18628,19 @@
         <v>23</v>
       </c>
       <c r="K287" s="0" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="L287" s="0" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="M287" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N287" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="O287" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="P287" s="0" t="s">
         <v>31</v>
@@ -18613,24 +18652,27 @@
         <v>33</v>
       </c>
       <c r="S287" s="0" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="0" t="s">
-        <v>568</v>
+        <v>571</v>
+      </c>
+      <c r="B288" s="0" t="s">
+        <v>572</v>
       </c>
       <c r="C288" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D288" s="0" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E288" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F288" s="0" t="s">
-        <v>23</v>
+        <v>158</v>
       </c>
       <c r="G288" s="0" t="s">
         <v>24</v>
@@ -18645,19 +18687,19 @@
         <v>23</v>
       </c>
       <c r="K288" s="0" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="L288" s="0" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="M288" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N288" s="0" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="O288" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="P288" s="0" t="s">
         <v>31</v>
@@ -18669,24 +18711,27 @@
         <v>33</v>
       </c>
       <c r="S288" s="0" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="0" t="s">
-        <v>568</v>
+        <v>573</v>
+      </c>
+      <c r="B289" s="0" t="s">
+        <v>574</v>
       </c>
       <c r="C289" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D289" s="0" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E289" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F289" s="0" t="s">
-        <v>23</v>
+        <v>121</v>
       </c>
       <c r="G289" s="0" t="s">
         <v>24</v>
@@ -18701,19 +18746,19 @@
         <v>23</v>
       </c>
       <c r="K289" s="0" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="L289" s="0" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="M289" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N289" s="0" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="O289" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="P289" s="0" t="s">
         <v>31</v>
@@ -18725,24 +18770,27 @@
         <v>33</v>
       </c>
       <c r="S289" s="0" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="0" t="s">
-        <v>568</v>
+        <v>575</v>
+      </c>
+      <c r="B290" s="0" t="s">
+        <v>576</v>
       </c>
       <c r="C290" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D290" s="0" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E290" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F290" s="0" t="s">
-        <v>23</v>
+        <v>483</v>
       </c>
       <c r="G290" s="0" t="s">
         <v>24</v>
@@ -18757,19 +18805,19 @@
         <v>23</v>
       </c>
       <c r="K290" s="0" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="L290" s="0" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="M290" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N290" s="0" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="O290" s="0" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="P290" s="0" t="s">
         <v>31</v>
@@ -18781,27 +18829,27 @@
         <v>33</v>
       </c>
       <c r="S290" s="0" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="0" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="B291" s="0" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="C291" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D291" s="0" t="s">
-        <v>44</v>
+        <v>154</v>
       </c>
       <c r="E291" s="0" t="s">
         <v>45</v>
       </c>
       <c r="F291" s="0" t="s">
-        <v>397</v>
+        <v>579</v>
       </c>
       <c r="G291" s="0" t="s">
         <v>24</v>
@@ -18819,16 +18867,16 @@
         <v>26</v>
       </c>
       <c r="L291" s="0" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="M291" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N291" s="0" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="O291" s="0" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="P291" s="0" t="s">
         <v>31</v>
@@ -18840,24 +18888,27 @@
         <v>33</v>
       </c>
       <c r="S291" s="0" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="0" t="s">
-        <v>571</v>
+        <v>580</v>
+      </c>
+      <c r="B292" s="0" t="s">
+        <v>581</v>
       </c>
       <c r="C292" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D292" s="0" t="s">
-        <v>137</v>
+        <v>44</v>
       </c>
       <c r="E292" s="0" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F292" s="0" t="s">
-        <v>23</v>
+        <v>288</v>
       </c>
       <c r="G292" s="0" t="s">
         <v>24</v>
@@ -18901,16 +18952,16 @@
     </row>
     <row r="293">
       <c r="A293" s="0" t="s">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="C293" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D293" s="0" t="s">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="E293" s="0" t="s">
-        <v>151</v>
+        <v>22</v>
       </c>
       <c r="F293" s="0" t="s">
         <v>23</v>
@@ -18928,19 +18979,19 @@
         <v>23</v>
       </c>
       <c r="K293" s="0" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="L293" s="0" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="M293" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N293" s="0" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="O293" s="0" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="P293" s="0" t="s">
         <v>31</v>
@@ -18952,27 +19003,24 @@
         <v>33</v>
       </c>
       <c r="S293" s="0" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="0" t="s">
-        <v>573</v>
-      </c>
-      <c r="B294" s="0" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="C294" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D294" s="0" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="E294" s="0" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="F294" s="0" t="s">
-        <v>575</v>
+        <v>23</v>
       </c>
       <c r="G294" s="0" t="s">
         <v>24</v>
@@ -18987,19 +19035,19 @@
         <v>23</v>
       </c>
       <c r="K294" s="0" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="L294" s="0" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="M294" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N294" s="0" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="O294" s="0" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="P294" s="0" t="s">
         <v>31</v>
@@ -19011,27 +19059,24 @@
         <v>33</v>
       </c>
       <c r="S294" s="0" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="0" t="s">
-        <v>576</v>
-      </c>
-      <c r="B295" s="0" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="C295" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D295" s="0" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E295" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F295" s="0" t="s">
-        <v>108</v>
+        <v>23</v>
       </c>
       <c r="G295" s="0" t="s">
         <v>24</v>
@@ -19046,19 +19091,19 @@
         <v>23</v>
       </c>
       <c r="K295" s="0" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="L295" s="0" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="M295" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N295" s="0" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="O295" s="0" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="P295" s="0" t="s">
         <v>31</v>
@@ -19070,15 +19115,15 @@
         <v>33</v>
       </c>
       <c r="S295" s="0" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="0" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="B296" s="0" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C296" s="0" t="s">
         <v>20</v>
@@ -19087,10 +19132,10 @@
         <v>44</v>
       </c>
       <c r="E296" s="0" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F296" s="0" t="s">
-        <v>580</v>
+        <v>397</v>
       </c>
       <c r="G296" s="0" t="s">
         <v>24</v>
@@ -19108,16 +19153,16 @@
         <v>26</v>
       </c>
       <c r="L296" s="0" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="M296" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N296" s="0" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="O296" s="0" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="P296" s="0" t="s">
         <v>31</v>
@@ -19129,27 +19174,24 @@
         <v>33</v>
       </c>
       <c r="S296" s="0" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="0" t="s">
-        <v>581</v>
-      </c>
-      <c r="B297" s="0" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C297" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D297" s="0" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="E297" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F297" s="0" t="s">
-        <v>583</v>
+        <v>23</v>
       </c>
       <c r="G297" s="0" t="s">
         <v>24</v>
@@ -19167,16 +19209,16 @@
         <v>26</v>
       </c>
       <c r="L297" s="0" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="M297" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N297" s="0" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="O297" s="0" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="P297" s="0" t="s">
         <v>31</v>
@@ -19188,27 +19230,24 @@
         <v>33</v>
       </c>
       <c r="S297" s="0" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="0" t="s">
-        <v>584</v>
-      </c>
-      <c r="B298" s="0" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C298" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D298" s="0" t="s">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="E298" s="0" t="s">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="F298" s="0" t="s">
-        <v>586</v>
+        <v>23</v>
       </c>
       <c r="G298" s="0" t="s">
         <v>24</v>
@@ -19226,16 +19265,16 @@
         <v>26</v>
       </c>
       <c r="L298" s="0" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="M298" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N298" s="0" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="O298" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="P298" s="0" t="s">
         <v>31</v>
@@ -19247,24 +19286,27 @@
         <v>33</v>
       </c>
       <c r="S298" s="0" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="0" t="s">
         <v>587</v>
       </c>
+      <c r="B299" s="0" t="s">
+        <v>588</v>
+      </c>
       <c r="C299" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D299" s="0" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="E299" s="0" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F299" s="0" t="s">
-        <v>23</v>
+        <v>589</v>
       </c>
       <c r="G299" s="0" t="s">
         <v>24</v>
@@ -19279,19 +19321,19 @@
         <v>23</v>
       </c>
       <c r="K299" s="0" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="L299" s="0" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="M299" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N299" s="0" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="O299" s="0" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="P299" s="0" t="s">
         <v>31</v>
@@ -19303,27 +19345,27 @@
         <v>33</v>
       </c>
       <c r="S299" s="0" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="0" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B300" s="0" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C300" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D300" s="0" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E300" s="0" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F300" s="0" t="s">
-        <v>590</v>
+        <v>108</v>
       </c>
       <c r="G300" s="0" t="s">
         <v>24</v>
@@ -19341,7 +19383,7 @@
         <v>26</v>
       </c>
       <c r="L300" s="0" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="M300" s="0" t="s">
         <v>28</v>
@@ -19367,19 +19409,22 @@
     </row>
     <row r="301">
       <c r="A301" s="0" t="s">
-        <v>591</v>
+        <v>592</v>
+      </c>
+      <c r="B301" s="0" t="s">
+        <v>593</v>
       </c>
       <c r="C301" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D301" s="0" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E301" s="0" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F301" s="0" t="s">
-        <v>23</v>
+        <v>594</v>
       </c>
       <c r="G301" s="0" t="s">
         <v>24</v>
@@ -19394,19 +19439,19 @@
         <v>23</v>
       </c>
       <c r="K301" s="0" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="L301" s="0" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="M301" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N301" s="0" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="O301" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="P301" s="0" t="s">
         <v>31</v>
@@ -19418,15 +19463,15 @@
         <v>33</v>
       </c>
       <c r="S301" s="0" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="0" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="B302" s="0" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C302" s="0" t="s">
         <v>20</v>
@@ -19435,10 +19480,10 @@
         <v>44</v>
       </c>
       <c r="E302" s="0" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F302" s="0" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="G302" s="0" t="s">
         <v>24</v>
@@ -19453,19 +19498,19 @@
         <v>23</v>
       </c>
       <c r="K302" s="0" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="L302" s="0" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="M302" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N302" s="0" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="O302" s="0" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="P302" s="0" t="s">
         <v>31</v>
@@ -19477,15 +19522,15 @@
         <v>33</v>
       </c>
       <c r="S302" s="0" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="0" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B303" s="0" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C303" s="0" t="s">
         <v>20</v>
@@ -19494,10 +19539,10 @@
         <v>44</v>
       </c>
       <c r="E303" s="0" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="F303" s="0" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="G303" s="0" t="s">
         <v>24</v>
@@ -19541,22 +19586,19 @@
     </row>
     <row r="304">
       <c r="A304" s="0" t="s">
-        <v>598</v>
-      </c>
-      <c r="B304" s="0" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C304" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D304" s="0" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="E304" s="0" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="F304" s="0" t="s">
-        <v>327</v>
+        <v>23</v>
       </c>
       <c r="G304" s="0" t="s">
         <v>24</v>
@@ -19571,19 +19613,19 @@
         <v>23</v>
       </c>
       <c r="K304" s="0" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="L304" s="0" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="M304" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N304" s="0" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="O304" s="0" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="P304" s="0" t="s">
         <v>31</v>
@@ -19595,27 +19637,27 @@
         <v>33</v>
       </c>
       <c r="S304" s="0" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="0" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B305" s="0" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C305" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D305" s="0" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E305" s="0" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="F305" s="0" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="G305" s="0" t="s">
         <v>24</v>
@@ -19633,7 +19675,7 @@
         <v>26</v>
       </c>
       <c r="L305" s="0" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="M305" s="0" t="s">
         <v>28</v>
@@ -19659,13 +19701,13 @@
     </row>
     <row r="306">
       <c r="A306" s="0" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C306" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D306" s="0" t="s">
-        <v>137</v>
+        <v>35</v>
       </c>
       <c r="E306" s="0" t="s">
         <v>22</v>
@@ -19686,19 +19728,19 @@
         <v>23</v>
       </c>
       <c r="K306" s="0" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="L306" s="0" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="M306" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N306" s="0" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="O306" s="0" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="P306" s="0" t="s">
         <v>31</v>
@@ -19710,24 +19752,27 @@
         <v>33</v>
       </c>
       <c r="S306" s="0" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="0" t="s">
-        <v>603</v>
+        <v>606</v>
+      </c>
+      <c r="B307" s="0" t="s">
+        <v>607</v>
       </c>
       <c r="C307" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D307" s="0" t="s">
-        <v>137</v>
+        <v>44</v>
       </c>
       <c r="E307" s="0" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F307" s="0" t="s">
-        <v>23</v>
+        <v>608</v>
       </c>
       <c r="G307" s="0" t="s">
         <v>24</v>
@@ -19742,19 +19787,19 @@
         <v>23</v>
       </c>
       <c r="K307" s="0" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="L307" s="0" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="M307" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N307" s="0" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="O307" s="0" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="P307" s="0" t="s">
         <v>31</v>
@@ -19766,24 +19811,27 @@
         <v>33</v>
       </c>
       <c r="S307" s="0" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="0" t="s">
-        <v>603</v>
+        <v>609</v>
+      </c>
+      <c r="B308" s="0" t="s">
+        <v>610</v>
       </c>
       <c r="C308" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D308" s="0" t="s">
-        <v>137</v>
+        <v>44</v>
       </c>
       <c r="E308" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F308" s="0" t="s">
-        <v>23</v>
+        <v>611</v>
       </c>
       <c r="G308" s="0" t="s">
         <v>24</v>
@@ -19801,16 +19849,16 @@
         <v>26</v>
       </c>
       <c r="L308" s="0" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="M308" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N308" s="0" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="O308" s="0" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="P308" s="0" t="s">
         <v>31</v>
@@ -19822,24 +19870,27 @@
         <v>33</v>
       </c>
       <c r="S308" s="0" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="0" t="s">
-        <v>604</v>
+        <v>612</v>
+      </c>
+      <c r="B309" s="0" t="s">
+        <v>613</v>
       </c>
       <c r="C309" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D309" s="0" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="E309" s="0" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F309" s="0" t="s">
-        <v>23</v>
+        <v>327</v>
       </c>
       <c r="G309" s="0" t="s">
         <v>24</v>
@@ -19857,16 +19908,16 @@
         <v>26</v>
       </c>
       <c r="L309" s="0" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="M309" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N309" s="0" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="O309" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="P309" s="0" t="s">
         <v>31</v>
@@ -19878,15 +19929,15 @@
         <v>33</v>
       </c>
       <c r="S309" s="0" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="0" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="B310" s="0" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="C310" s="0" t="s">
         <v>20</v>
@@ -19898,7 +19949,7 @@
         <v>45</v>
       </c>
       <c r="F310" s="0" t="s">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="G310" s="0" t="s">
         <v>24</v>
@@ -19913,19 +19964,19 @@
         <v>23</v>
       </c>
       <c r="K310" s="0" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="L310" s="0" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="M310" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N310" s="0" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="O310" s="0" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="P310" s="0" t="s">
         <v>31</v>
@@ -19937,27 +19988,24 @@
         <v>33</v>
       </c>
       <c r="S310" s="0" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="0" t="s">
-        <v>608</v>
-      </c>
-      <c r="B311" s="0" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="C311" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D311" s="0" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="E311" s="0" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="F311" s="0" t="s">
-        <v>501</v>
+        <v>23</v>
       </c>
       <c r="G311" s="0" t="s">
         <v>24</v>
@@ -19975,16 +20023,16 @@
         <v>26</v>
       </c>
       <c r="L311" s="0" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="M311" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N311" s="0" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="O311" s="0" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="P311" s="0" t="s">
         <v>31</v>
@@ -19996,27 +20044,24 @@
         <v>33</v>
       </c>
       <c r="S311" s="0" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="0" t="s">
-        <v>610</v>
-      </c>
-      <c r="B312" s="0" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="C312" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D312" s="0" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="E312" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F312" s="0" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="G312" s="0" t="s">
         <v>24</v>
@@ -20034,16 +20079,16 @@
         <v>26</v>
       </c>
       <c r="L312" s="0" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="M312" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N312" s="0" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="O312" s="0" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="P312" s="0" t="s">
         <v>31</v>
@@ -20055,18 +20100,18 @@
         <v>33</v>
       </c>
       <c r="S312" s="0" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="0" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="C313" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D313" s="0" t="s">
-        <v>35</v>
+        <v>137</v>
       </c>
       <c r="E313" s="0" t="s">
         <v>22</v>
@@ -20090,16 +20135,16 @@
         <v>26</v>
       </c>
       <c r="L313" s="0" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="M313" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N313" s="0" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="O313" s="0" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="P313" s="0" t="s">
         <v>31</v>
@@ -20111,12 +20156,12 @@
         <v>33</v>
       </c>
       <c r="S313" s="0" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="0" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="C314" s="0" t="s">
         <v>20</v>
@@ -20172,22 +20217,22 @@
     </row>
     <row r="315">
       <c r="A315" s="0" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="B315" s="0" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="C315" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D315" s="0" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E315" s="0" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F315" s="0" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="G315" s="0" t="s">
         <v>24</v>
@@ -20202,19 +20247,19 @@
         <v>23</v>
       </c>
       <c r="K315" s="0" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="L315" s="0" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="M315" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N315" s="0" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="O315" s="0" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="P315" s="0" t="s">
         <v>31</v>
@@ -20226,27 +20271,27 @@
         <v>33</v>
       </c>
       <c r="S315" s="0" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="0" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="B316" s="0" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="C316" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D316" s="0" t="s">
-        <v>154</v>
+        <v>44</v>
       </c>
       <c r="E316" s="0" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="F316" s="0" t="s">
-        <v>583</v>
+        <v>515</v>
       </c>
       <c r="G316" s="0" t="s">
         <v>24</v>
@@ -20264,16 +20309,16 @@
         <v>26</v>
       </c>
       <c r="L316" s="0" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="M316" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N316" s="0" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="O316" s="0" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="P316" s="0" t="s">
         <v>31</v>
@@ -20285,24 +20330,27 @@
         <v>33</v>
       </c>
       <c r="S316" s="0" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="0" t="s">
-        <v>618</v>
+        <v>624</v>
+      </c>
+      <c r="B317" s="0" t="s">
+        <v>625</v>
       </c>
       <c r="C317" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D317" s="0" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E317" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F317" s="0" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="G317" s="0" t="s">
         <v>24</v>
@@ -20320,7 +20368,7 @@
         <v>26</v>
       </c>
       <c r="L317" s="0" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="M317" s="0" t="s">
         <v>28</v>
@@ -20346,13 +20394,13 @@
     </row>
     <row r="318">
       <c r="A318" s="0" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="C318" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D318" s="0" t="s">
-        <v>137</v>
+        <v>35</v>
       </c>
       <c r="E318" s="0" t="s">
         <v>22</v>
@@ -20402,13 +20450,13 @@
     </row>
     <row r="319">
       <c r="A319" s="0" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="C319" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D319" s="0" t="s">
-        <v>137</v>
+        <v>35</v>
       </c>
       <c r="E319" s="0" t="s">
         <v>22</v>
@@ -20458,22 +20506,22 @@
     </row>
     <row r="320">
       <c r="A320" s="0" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="B320" s="0" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="C320" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D320" s="0" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E320" s="0" t="s">
         <v>70</v>
       </c>
       <c r="F320" s="0" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="G320" s="0" t="s">
         <v>24</v>
@@ -20491,16 +20539,16 @@
         <v>26</v>
       </c>
       <c r="L320" s="0" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="M320" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N320" s="0" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="O320" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="P320" s="0" t="s">
         <v>31</v>
@@ -20512,27 +20560,27 @@
         <v>33</v>
       </c>
       <c r="S320" s="0" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="0" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="B321" s="0" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="C321" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D321" s="0" t="s">
-        <v>44</v>
+        <v>154</v>
       </c>
       <c r="E321" s="0" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F321" s="0" t="s">
-        <v>203</v>
+        <v>597</v>
       </c>
       <c r="G321" s="0" t="s">
         <v>24</v>
@@ -20550,16 +20598,16 @@
         <v>26</v>
       </c>
       <c r="L321" s="0" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="M321" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N321" s="0" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="O321" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="P321" s="0" t="s">
         <v>31</v>
@@ -20571,27 +20619,24 @@
         <v>33</v>
       </c>
       <c r="S321" s="0" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="0" t="s">
-        <v>625</v>
-      </c>
-      <c r="B322" s="0" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="C322" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D322" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E322" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F322" s="0" t="s">
-        <v>423</v>
+        <v>23</v>
       </c>
       <c r="G322" s="0" t="s">
         <v>24</v>
@@ -20609,7 +20654,7 @@
         <v>26</v>
       </c>
       <c r="L322" s="0" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="M322" s="0" t="s">
         <v>28</v>
@@ -20635,13 +20680,13 @@
     </row>
     <row r="323">
       <c r="A323" s="0" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="C323" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D323" s="0" t="s">
-        <v>35</v>
+        <v>137</v>
       </c>
       <c r="E323" s="0" t="s">
         <v>22</v>
@@ -20691,22 +20736,19 @@
     </row>
     <row r="324">
       <c r="A324" s="0" t="s">
-        <v>628</v>
-      </c>
-      <c r="B324" s="0" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="C324" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D324" s="0" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="E324" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F324" s="0" t="s">
-        <v>630</v>
+        <v>23</v>
       </c>
       <c r="G324" s="0" t="s">
         <v>24</v>
@@ -20724,7 +20766,7 @@
         <v>26</v>
       </c>
       <c r="L324" s="0" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="M324" s="0" t="s">
         <v>28</v>
@@ -20750,22 +20792,22 @@
     </row>
     <row r="325">
       <c r="A325" s="0" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="B325" s="0" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C325" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D325" s="0" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="E325" s="0" t="s">
         <v>70</v>
       </c>
       <c r="F325" s="0" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="G325" s="0" t="s">
         <v>24</v>
@@ -20809,10 +20851,10 @@
     </row>
     <row r="326">
       <c r="A326" s="0" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B326" s="0" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C326" s="0" t="s">
         <v>20</v>
@@ -20821,10 +20863,10 @@
         <v>44</v>
       </c>
       <c r="E326" s="0" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="F326" s="0" t="s">
-        <v>636</v>
+        <v>203</v>
       </c>
       <c r="G326" s="0" t="s">
         <v>24</v>
@@ -20868,22 +20910,22 @@
     </row>
     <row r="327">
       <c r="A327" s="0" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B327" s="0" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C327" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D327" s="0" t="s">
-        <v>154</v>
+        <v>44</v>
       </c>
       <c r="E327" s="0" t="s">
         <v>45</v>
       </c>
       <c r="F327" s="0" t="s">
-        <v>639</v>
+        <v>423</v>
       </c>
       <c r="G327" s="0" t="s">
         <v>24</v>
@@ -20901,16 +20943,16 @@
         <v>26</v>
       </c>
       <c r="L327" s="0" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="M327" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N327" s="0" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="O327" s="0" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="P327" s="0" t="s">
         <v>31</v>
@@ -20922,18 +20964,18 @@
         <v>33</v>
       </c>
       <c r="S327" s="0" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="0" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C328" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D328" s="0" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E328" s="0" t="s">
         <v>22</v>
@@ -20983,19 +21025,22 @@
     </row>
     <row r="329">
       <c r="A329" s="0" t="s">
-        <v>640</v>
+        <v>642</v>
+      </c>
+      <c r="B329" s="0" t="s">
+        <v>643</v>
       </c>
       <c r="C329" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D329" s="0" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E329" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F329" s="0" t="s">
-        <v>23</v>
+        <v>644</v>
       </c>
       <c r="G329" s="0" t="s">
         <v>24</v>
@@ -21013,7 +21058,7 @@
         <v>26</v>
       </c>
       <c r="L329" s="0" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="M329" s="0" t="s">
         <v>28</v>
@@ -21039,19 +21084,22 @@
     </row>
     <row r="330">
       <c r="A330" s="0" t="s">
-        <v>640</v>
+        <v>645</v>
+      </c>
+      <c r="B330" s="0" t="s">
+        <v>646</v>
       </c>
       <c r="C330" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D330" s="0" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="E330" s="0" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F330" s="0" t="s">
-        <v>23</v>
+        <v>647</v>
       </c>
       <c r="G330" s="0" t="s">
         <v>24</v>
@@ -21069,7 +21117,7 @@
         <v>26</v>
       </c>
       <c r="L330" s="0" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="M330" s="0" t="s">
         <v>28</v>
@@ -21095,10 +21143,10 @@
     </row>
     <row r="331">
       <c r="A331" s="0" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="B331" s="0" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="C331" s="0" t="s">
         <v>20</v>
@@ -21110,7 +21158,7 @@
         <v>45</v>
       </c>
       <c r="F331" s="0" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="G331" s="0" t="s">
         <v>24</v>
@@ -21128,7 +21176,7 @@
         <v>26</v>
       </c>
       <c r="L331" s="0" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="M331" s="0" t="s">
         <v>28</v>
@@ -21154,19 +21202,22 @@
     </row>
     <row r="332">
       <c r="A332" s="0" t="s">
-        <v>644</v>
+        <v>651</v>
+      </c>
+      <c r="B332" s="0" t="s">
+        <v>652</v>
       </c>
       <c r="C332" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D332" s="0" t="s">
-        <v>35</v>
+        <v>154</v>
       </c>
       <c r="E332" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F332" s="0" t="s">
-        <v>23</v>
+        <v>653</v>
       </c>
       <c r="G332" s="0" t="s">
         <v>24</v>
@@ -21184,16 +21235,16 @@
         <v>26</v>
       </c>
       <c r="L332" s="0" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="M332" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N332" s="0" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="O332" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="P332" s="0" t="s">
         <v>31</v>
@@ -21205,18 +21256,18 @@
         <v>33</v>
       </c>
       <c r="S332" s="0" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="0" t="s">
-        <v>644</v>
+        <v>654</v>
       </c>
       <c r="C333" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D333" s="0" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E333" s="0" t="s">
         <v>22</v>
@@ -21266,13 +21317,13 @@
     </row>
     <row r="334">
       <c r="A334" s="0" t="s">
-        <v>644</v>
+        <v>654</v>
       </c>
       <c r="C334" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D334" s="0" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E334" s="0" t="s">
         <v>22</v>
@@ -21322,22 +21373,19 @@
     </row>
     <row r="335">
       <c r="A335" s="0" t="s">
-        <v>645</v>
-      </c>
-      <c r="B335" s="0" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="C335" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D335" s="0" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="E335" s="0" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="F335" s="0" t="s">
-        <v>647</v>
+        <v>23</v>
       </c>
       <c r="G335" s="0" t="s">
         <v>24</v>
@@ -21355,16 +21403,16 @@
         <v>26</v>
       </c>
       <c r="L335" s="0" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="M335" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N335" s="0" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="O335" s="0" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="P335" s="0" t="s">
         <v>31</v>
@@ -21376,24 +21424,27 @@
         <v>33</v>
       </c>
       <c r="S335" s="0" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="0" t="s">
-        <v>648</v>
+        <v>655</v>
+      </c>
+      <c r="B336" s="0" t="s">
+        <v>656</v>
       </c>
       <c r="C336" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D336" s="0" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E336" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F336" s="0" t="s">
-        <v>23</v>
+        <v>657</v>
       </c>
       <c r="G336" s="0" t="s">
         <v>24</v>
@@ -21411,16 +21462,16 @@
         <v>26</v>
       </c>
       <c r="L336" s="0" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="M336" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N336" s="0" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="O336" s="0" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="P336" s="0" t="s">
         <v>31</v>
@@ -21432,27 +21483,24 @@
         <v>33</v>
       </c>
       <c r="S336" s="0" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="0" t="s">
-        <v>649</v>
-      </c>
-      <c r="B337" s="0" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="C337" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D337" s="0" t="s">
-        <v>154</v>
+        <v>35</v>
       </c>
       <c r="E337" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F337" s="0" t="s">
-        <v>651</v>
+        <v>23</v>
       </c>
       <c r="G337" s="0" t="s">
         <v>24</v>
@@ -21470,16 +21518,16 @@
         <v>26</v>
       </c>
       <c r="L337" s="0" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="M337" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N337" s="0" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="O337" s="0" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="P337" s="0" t="s">
         <v>31</v>
@@ -21491,27 +21539,24 @@
         <v>33</v>
       </c>
       <c r="S337" s="0" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="0" t="s">
-        <v>652</v>
-      </c>
-      <c r="B338" s="0" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="C338" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D338" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E338" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F338" s="0" t="s">
-        <v>654</v>
+        <v>23</v>
       </c>
       <c r="G338" s="0" t="s">
         <v>24</v>
@@ -21555,13 +21600,13 @@
     </row>
     <row r="339">
       <c r="A339" s="0" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C339" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D339" s="0" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E339" s="0" t="s">
         <v>22</v>
@@ -21585,16 +21630,16 @@
         <v>26</v>
       </c>
       <c r="L339" s="0" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="M339" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N339" s="0" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="O339" s="0" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="P339" s="0" t="s">
         <v>31</v>
@@ -21606,24 +21651,27 @@
         <v>33</v>
       </c>
       <c r="S339" s="0" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="0" t="s">
-        <v>655</v>
+        <v>659</v>
+      </c>
+      <c r="B340" s="0" t="s">
+        <v>660</v>
       </c>
       <c r="C340" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D340" s="0" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="E340" s="0" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F340" s="0" t="s">
-        <v>23</v>
+        <v>661</v>
       </c>
       <c r="G340" s="0" t="s">
         <v>24</v>
@@ -21641,16 +21689,16 @@
         <v>26</v>
       </c>
       <c r="L340" s="0" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="M340" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N340" s="0" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="O340" s="0" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="P340" s="0" t="s">
         <v>31</v>
@@ -21662,18 +21710,18 @@
         <v>33</v>
       </c>
       <c r="S340" s="0" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="0" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="C341" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D341" s="0" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E341" s="0" t="s">
         <v>22</v>
@@ -21697,16 +21745,16 @@
         <v>26</v>
       </c>
       <c r="L341" s="0" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="M341" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N341" s="0" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="O341" s="0" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="P341" s="0" t="s">
         <v>31</v>
@@ -21718,27 +21766,27 @@
         <v>33</v>
       </c>
       <c r="S341" s="0" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="0" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="B342" s="0" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="C342" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D342" s="0" t="s">
-        <v>74</v>
+        <v>154</v>
       </c>
       <c r="E342" s="0" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F342" s="0" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="G342" s="0" t="s">
         <v>24</v>
@@ -21782,10 +21830,10 @@
     </row>
     <row r="343">
       <c r="A343" s="0" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="B343" s="0" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="C343" s="0" t="s">
         <v>20</v>
@@ -21797,7 +21845,7 @@
         <v>45</v>
       </c>
       <c r="F343" s="0" t="s">
-        <v>661</v>
+        <v>442</v>
       </c>
       <c r="G343" s="0" t="s">
         <v>24</v>
@@ -21815,7 +21863,7 @@
         <v>26</v>
       </c>
       <c r="L343" s="0" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="M343" s="0" t="s">
         <v>28</v>
@@ -21841,13 +21889,13 @@
     </row>
     <row r="344">
       <c r="A344" s="0" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="C344" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D344" s="0" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E344" s="0" t="s">
         <v>22</v>
@@ -21871,16 +21919,16 @@
         <v>26</v>
       </c>
       <c r="L344" s="0" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="M344" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N344" s="0" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="O344" s="0" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="P344" s="0" t="s">
         <v>31</v>
@@ -21892,27 +21940,24 @@
         <v>33</v>
       </c>
       <c r="S344" s="0" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="0" t="s">
-        <v>663</v>
-      </c>
-      <c r="B345" s="0" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="C345" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D345" s="0" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E345" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F345" s="0" t="s">
-        <v>639</v>
+        <v>23</v>
       </c>
       <c r="G345" s="0" t="s">
         <v>24</v>
@@ -21930,16 +21975,16 @@
         <v>26</v>
       </c>
       <c r="L345" s="0" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="M345" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N345" s="0" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="O345" s="0" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="P345" s="0" t="s">
         <v>31</v>
@@ -21951,18 +21996,18 @@
         <v>33</v>
       </c>
       <c r="S345" s="0" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="0" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C346" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D346" s="0" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E346" s="0" t="s">
         <v>22</v>
@@ -21986,16 +22031,16 @@
         <v>26</v>
       </c>
       <c r="L346" s="0" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="M346" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N346" s="0" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="O346" s="0" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="P346" s="0" t="s">
         <v>31</v>
@@ -22007,24 +22052,27 @@
         <v>33</v>
       </c>
       <c r="S346" s="0" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="0" t="s">
-        <v>665</v>
+        <v>669</v>
+      </c>
+      <c r="B347" s="0" t="s">
+        <v>670</v>
       </c>
       <c r="C347" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D347" s="0" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="E347" s="0" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F347" s="0" t="s">
-        <v>23</v>
+        <v>671</v>
       </c>
       <c r="G347" s="0" t="s">
         <v>24</v>
@@ -22042,16 +22090,16 @@
         <v>26</v>
       </c>
       <c r="L347" s="0" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="M347" s="0" t="s">
         <v>28</v>
       </c>
       <c r="N347" s="0" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="O347" s="0" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="P347" s="0" t="s">
         <v>31</v>
@@ -22063,15 +22111,15 @@
         <v>33</v>
       </c>
       <c r="S347" s="0" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="0" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="B348" s="0" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="C348" s="0" t="s">
         <v>20</v>
@@ -22080,10 +22128,10 @@
         <v>44</v>
       </c>
       <c r="E348" s="0" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F348" s="0" t="s">
-        <v>630</v>
+        <v>674</v>
       </c>
       <c r="G348" s="0" t="s">
         <v>24</v>
@@ -22127,22 +22175,19 @@
     </row>
     <row r="349">
       <c r="A349" s="0" t="s">
-        <v>668</v>
-      </c>
-      <c r="B349" s="0" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="C349" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D349" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E349" s="0" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="F349" s="0" t="s">
-        <v>633</v>
+        <v>23</v>
       </c>
       <c r="G349" s="0" t="s">
         <v>24</v>
@@ -22186,19 +22231,22 @@
     </row>
     <row r="350">
       <c r="A350" s="0" t="s">
-        <v>670</v>
+        <v>676</v>
+      </c>
+      <c r="B350" s="0" t="s">
+        <v>677</v>
       </c>
       <c r="C350" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D350" s="0" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E350" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F350" s="0" t="s">
-        <v>23</v>
+        <v>653</v>
       </c>
       <c r="G350" s="0" t="s">
         <v>24</v>
@@ -22242,22 +22290,19 @@
     </row>
     <row r="351">
       <c r="A351" s="0" t="s">
-        <v>671</v>
-      </c>
-      <c r="B351" s="0" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="C351" s="0" t="s">
         <v>20</v>
       </c>
       <c r="D351" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E351" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F351" s="0" t="s">
-        <v>673</v>
+        <v>23</v>
       </c>
       <c r="G351" s="0" t="s">
         <v>24</v>
@@ -22275,27 +22320,316 @@
         <v>26</v>
       </c>
       <c r="L351" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="M351" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="N351" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="O351" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="P351" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q351" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R351" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="S351" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="0" t="s">
+        <v>678</v>
+      </c>
+      <c r="C352" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="D352" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="E352" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="F352" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G352" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="H352" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="I352" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="J352" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="K352" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="L352" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="M352" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="N352" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="O352" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="P352" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q352" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R352" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="S352" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="0" t="s">
+        <v>679</v>
+      </c>
+      <c r="B353" s="0" t="s">
+        <v>680</v>
+      </c>
+      <c r="C353" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="D353" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E353" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="F353" s="0" t="s">
+        <v>644</v>
+      </c>
+      <c r="G353" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="H353" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="I353" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="J353" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="K353" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="L353" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="M353" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="N353" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="O353" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="P353" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q353" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R353" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="S353" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="0" t="s">
+        <v>681</v>
+      </c>
+      <c r="B354" s="0" t="s">
+        <v>682</v>
+      </c>
+      <c r="C354" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="D354" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E354" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="F354" s="0" t="s">
+        <v>647</v>
+      </c>
+      <c r="G354" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="H354" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="I354" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="J354" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="K354" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="L354" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="M354" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="N354" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="O354" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="P354" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q354" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R354" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="S354" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="0" t="s">
+        <v>683</v>
+      </c>
+      <c r="C355" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="D355" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="E355" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="F355" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G355" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="H355" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="I355" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="J355" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="K355" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="L355" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="M355" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="N355" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="O355" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="P355" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q355" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R355" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="S355" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="0" t="s">
+        <v>684</v>
+      </c>
+      <c r="B356" s="0" t="s">
+        <v>685</v>
+      </c>
+      <c r="C356" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="D356" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E356" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="F356" s="0" t="s">
+        <v>686</v>
+      </c>
+      <c r="G356" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="H356" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="I356" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="J356" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="K356" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="L356" s="0" t="s">
         <v>86</v>
       </c>
-      <c r="M351" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="N351" s="0" t="s">
+      <c r="M356" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="N356" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="O351" s="0" t="s">
+      <c r="O356" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="P351" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q351" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="R351" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="S351" s="0" t="s">
+      <c r="P356" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q356" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R356" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="S356" s="0" t="s">
         <v>56</v>
       </c>
     </row>
